--- a/src/ExcelsiorAspose.Tests/FilterTests.DefaultOffWithOneOn.verified.xlsx
+++ b/src/ExcelsiorAspose.Tests/FilterTests.DefaultOffWithOneOn.verified.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="240" yWindow="120" windowWidth="14940" windowHeight="9225" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="2" r:id="DeterministicId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$3</definedName>

--- a/src/ExcelsiorAspose.Tests/FilterTests.DefaultOffWithOneOn.verified.xlsx
+++ b/src/ExcelsiorAspose.Tests/FilterTests.DefaultOffWithOneOn.verified.xlsx
@@ -486,7 +486,7 @@
     <col min="3" max="3" width="14.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="14" customHeight="1">
+    <row r="1" spans="1:3" ht="16" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -497,7 +497,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="14" customHeight="1">
+    <row r="2" spans="1:3" ht="16" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -508,7 +508,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="14" customHeight="1">
+    <row r="3" spans="1:3" ht="16" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>

--- a/src/ExcelsiorAspose.Tests/FilterTests.DefaultOffWithOneOn.verified.xlsx
+++ b/src/ExcelsiorAspose.Tests/FilterTests.DefaultOffWithOneOn.verified.xlsx
@@ -486,7 +486,7 @@
     <col min="3" max="3" width="14.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16" customHeight="1">
+    <row r="1" spans="1:3" ht="14" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -497,7 +497,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="16" customHeight="1">
+    <row r="2" spans="1:3" ht="14" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -508,7 +508,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="16" customHeight="1">
+    <row r="3" spans="1:3" ht="14" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
